--- a/outputs/daily/hr_rankings_2026-08-17.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-17.xlsx
@@ -33185,32 +33185,32 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>665877</t>
+          <t>605170</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>José Fermín</t>
+          <t>Victor Caratini</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-08-17T17:40:00Z</t>
+          <t>2026-08-17T23:40:00Z</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -33220,12 +33220,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Kent Emanuel</t>
+          <t>Martín Pérez</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>592288</t>
+          <t>527048</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -33234,7 +33234,7 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>46.1</v>
+        <v>46.2</v>
       </c>
       <c r="M102" t="inlineStr">
         <is>
@@ -33248,26 +33248,26 @@
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>Good Environment, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P102" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="Q102" t="n">
-        <v>41.2</v>
+        <v>37.9</v>
       </c>
       <c r="R102" t="n">
-        <v>78.3</v>
+        <v>52.6</v>
       </c>
       <c r="S102" t="n">
-        <v>86.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T102" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U102" t="n">
-        <v>28.9</v>
+        <v>10.6</v>
       </c>
       <c r="V102" t="n">
         <v>50</v>
@@ -33275,42 +33275,42 @@
       <c r="W102" t="inlineStr"/>
       <c r="X102" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y102" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA102" t="inlineStr">
+      <c r="AB102" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
         </is>
       </c>
       <c r="AD102" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 9</t>
+          <t>lineup projected / unconfirmed</t>
         </is>
       </c>
       <c r="AE102" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF102" t="inlineStr"/>
@@ -33327,12 +33327,12 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL102" t="inlineStr">
@@ -33342,12 +33342,12 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/16, 0 HR</t>
+          <t>Last 7 games: 4/21, 0 HR</t>
         </is>
       </c>
       <c r="AN102" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.4% barrel, 9.5 HR allowed</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
@@ -33357,78 +33357,102 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AQ102" t="inlineStr">
         <is>
-          <t>31.43</t>
+          <t>39.86</t>
         </is>
       </c>
       <c r="AR102" t="inlineStr">
         <is>
-          <t>86.89</t>
+          <t>89.33</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr">
         <is>
-          <t>96.749</t>
+          <t>99.0024</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr">
         <is>
-          <t>0.3544</t>
+          <t>0.3963</t>
         </is>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>0.0934</t>
+          <t>0.1539</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>0.3124</t>
+          <t>0.3234</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>68.07</t>
+          <t>71.39</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>16.29</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>48.53</t>
+          <t>37.43</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>24.59</t>
+          <t>24.04</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>0.1207</t>
-        </is>
-      </c>
-      <c r="BC102" t="inlineStr"/>
-      <c r="BD102" t="inlineStr"/>
-      <c r="BE102" t="inlineStr"/>
-      <c r="BF102" t="inlineStr"/>
-      <c r="BG102" t="inlineStr"/>
-      <c r="BH102" t="inlineStr"/>
+          <t>0.1177</t>
+        </is>
+      </c>
+      <c r="BC102" t="inlineStr">
+        <is>
+          <t>8.42</t>
+        </is>
+      </c>
+      <c r="BD102" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="BE102" t="inlineStr">
+        <is>
+          <t>88.2</t>
+        </is>
+      </c>
+      <c r="BF102" t="inlineStr">
+        <is>
+          <t>0.4157</t>
+        </is>
+      </c>
+      <c r="BG102" t="inlineStr">
+        <is>
+          <t>0.1639</t>
+        </is>
+      </c>
+      <c r="BH102" t="inlineStr">
+        <is>
+          <t>24.27</t>
+        </is>
+      </c>
       <c r="BI102" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>330 deg</t>
         </is>
       </c>
       <c r="BJ102" t="inlineStr">
@@ -33438,27 +33462,27 @@
       </c>
       <c r="BK102" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=39.0979&amp;lon=-84.5082</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
         </is>
       </c>
       <c r="BL102" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>43</t>
         </is>
       </c>
       <c r="BM102" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN102" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BO102" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BP102" t="inlineStr"/>
@@ -33479,32 +33503,32 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>645277</t>
+          <t>665877</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>José Fermín</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-08-17T23:40:00Z</t>
+          <t>2026-08-17T17:40:00Z</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -33514,21 +33538,21 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Bailey Ober</t>
+          <t>Kent Emanuel</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>641927</t>
+          <t>592288</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>45.9</v>
+        <v>46.1</v>
       </c>
       <c r="M103" t="inlineStr">
         <is>
@@ -33542,26 +33566,26 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P103" t="n">
-        <v>17.2</v>
+        <v>11</v>
       </c>
       <c r="Q103" t="n">
-        <v>53.5</v>
+        <v>41.2</v>
       </c>
       <c r="R103" t="n">
-        <v>52.6</v>
+        <v>78.3</v>
       </c>
       <c r="S103" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T103" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U103" t="n">
-        <v>18.3</v>
+        <v>28.9</v>
       </c>
       <c r="V103" t="n">
         <v>50</v>
@@ -33569,17 +33593,17 @@
       <c r="W103" t="inlineStr"/>
       <c r="X103" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y103" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -33594,17 +33618,17 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD103" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 9</t>
         </is>
       </c>
       <c r="AE103" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AF103" t="inlineStr"/>
@@ -33621,132 +33645,108 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL103" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/23, 1 HR</t>
+          <t>Last 7 games: 5/16, 0 HR</t>
         </is>
       </c>
       <c r="AN103" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 10.7% barrel, 20.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="AQ103" t="inlineStr">
         <is>
-          <t>28.95</t>
+          <t>31.43</t>
         </is>
       </c>
       <c r="AR103" t="inlineStr">
         <is>
-          <t>87.08</t>
+          <t>86.89</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr">
         <is>
-          <t>96.7609</t>
+          <t>96.749</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr">
         <is>
-          <t>0.3611</t>
+          <t>0.3544</t>
         </is>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>0.1272</t>
+          <t>0.0934</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>0.2892</t>
+          <t>0.3124</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>68.86</t>
+          <t>68.07</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>46.77</t>
+          <t>48.53</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>24.59</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>18.8</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>0.1579</t>
-        </is>
-      </c>
-      <c r="BC103" t="inlineStr">
-        <is>
-          <t>10.69</t>
-        </is>
-      </c>
-      <c r="BD103" t="inlineStr">
-        <is>
-          <t>36.23</t>
-        </is>
-      </c>
-      <c r="BE103" t="inlineStr">
-        <is>
-          <t>88.83</t>
-        </is>
-      </c>
-      <c r="BF103" t="inlineStr">
-        <is>
-          <t>0.4669</t>
-        </is>
-      </c>
-      <c r="BG103" t="inlineStr">
-        <is>
-          <t>0.2147</t>
-        </is>
-      </c>
-      <c r="BH103" t="inlineStr">
-        <is>
-          <t>31.83</t>
-        </is>
-      </c>
+          <t>0.1207</t>
+        </is>
+      </c>
+      <c r="BC103" t="inlineStr"/>
+      <c r="BD103" t="inlineStr"/>
+      <c r="BE103" t="inlineStr"/>
+      <c r="BF103" t="inlineStr"/>
+      <c r="BG103" t="inlineStr"/>
+      <c r="BH103" t="inlineStr"/>
       <c r="BI103" t="inlineStr">
         <is>
-          <t>330 deg</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ103" t="inlineStr">
@@ -33756,27 +33756,27 @@
       </c>
       <c r="BK103" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=39.0979&amp;lon=-84.5082</t>
         </is>
       </c>
       <c r="BL103" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BM103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="BN103" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BO103" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BP103" t="inlineStr"/>
@@ -33797,27 +33797,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>672640</t>
+          <t>645277</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Otto Lopez</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-17T22:40:00Z</t>
+          <t>2026-08-17T23:40:00Z</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -33827,26 +33827,26 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Cristopher Sánchez</t>
+          <t>Bailey Ober</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>650911</t>
+          <t>641927</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>45.5</v>
+        <v>45.9</v>
       </c>
       <c r="M104" t="inlineStr">
         <is>
@@ -33860,26 +33860,26 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P104" t="n">
-        <v>29.8</v>
+        <v>17.2</v>
       </c>
       <c r="Q104" t="n">
-        <v>32.1</v>
+        <v>53.5</v>
       </c>
       <c r="R104" t="n">
-        <v>52.8</v>
+        <v>52.6</v>
       </c>
       <c r="S104" t="n">
-        <v>88.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T104" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U104" t="n">
-        <v>7</v>
+        <v>18.3</v>
       </c>
       <c r="V104" t="n">
         <v>50</v>
@@ -33897,7 +33897,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -33939,162 +33939,162 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AL104" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM104" t="inlineStr">
+        <is>
+          <t>Last 7 games: 2/23, 1 HR</t>
+        </is>
+      </c>
+      <c r="AN104" t="inlineStr">
+        <is>
+          <t>switch hitter; pitcher baseline 10.7% barrel, 20.9 HR allowed</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+        </is>
+      </c>
+      <c r="AP104" t="inlineStr">
+        <is>
+          <t>4.55</t>
+        </is>
+      </c>
+      <c r="AQ104" t="inlineStr">
+        <is>
+          <t>28.95</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>87.08</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr">
+        <is>
+          <t>96.7609</t>
+        </is>
+      </c>
+      <c r="AT104" t="inlineStr">
+        <is>
+          <t>0.3611</t>
+        </is>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>0.1272</t>
+        </is>
+      </c>
+      <c r="AV104" t="inlineStr">
+        <is>
+          <t>0.2892</t>
+        </is>
+      </c>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>68.86</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>46.77</t>
+        </is>
+      </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>32.32</t>
+        </is>
+      </c>
+      <c r="BA104" t="inlineStr">
+        <is>
+          <t>18.8</t>
+        </is>
+      </c>
+      <c r="BB104" t="inlineStr">
+        <is>
+          <t>0.1579</t>
+        </is>
+      </c>
+      <c r="BC104" t="inlineStr">
+        <is>
+          <t>10.69</t>
+        </is>
+      </c>
+      <c r="BD104" t="inlineStr">
+        <is>
+          <t>36.23</t>
+        </is>
+      </c>
+      <c r="BE104" t="inlineStr">
+        <is>
+          <t>88.83</t>
+        </is>
+      </c>
+      <c r="BF104" t="inlineStr">
+        <is>
+          <t>0.4669</t>
+        </is>
+      </c>
+      <c r="BG104" t="inlineStr">
+        <is>
+          <t>0.2147</t>
+        </is>
+      </c>
+      <c r="BH104" t="inlineStr">
+        <is>
+          <t>31.83</t>
+        </is>
+      </c>
+      <c r="BI104" t="inlineStr">
+        <is>
+          <t>330 deg</t>
+        </is>
+      </c>
+      <c r="BJ104" t="inlineStr">
+        <is>
+          <t>Open-Meteo forecast; MLB fallback</t>
+        </is>
+      </c>
+      <c r="BK104" t="inlineStr">
+        <is>
+          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
+        </is>
+      </c>
+      <c r="BL104" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="BM104" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>Last 7 games: 5/30, 0 HR</t>
-        </is>
-      </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>platoon edge; pitcher baseline 7.0% barrel, 12.7 HR allowed</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
-        </is>
-      </c>
-      <c r="AP104" t="inlineStr">
-        <is>
-          <t>6.4</t>
-        </is>
-      </c>
-      <c r="AQ104" t="inlineStr">
-        <is>
-          <t>40.26</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>88.85</t>
-        </is>
-      </c>
-      <c r="AS104" t="inlineStr">
-        <is>
-          <t>100.178</t>
-        </is>
-      </c>
-      <c r="AT104" t="inlineStr">
-        <is>
-          <t>0.4228</t>
-        </is>
-      </c>
-      <c r="AU104" t="inlineStr">
-        <is>
-          <t>0.1461</t>
-        </is>
-      </c>
-      <c r="AV104" t="inlineStr">
-        <is>
-          <t>0.3237</t>
-        </is>
-      </c>
-      <c r="AW104" t="inlineStr">
-        <is>
-          <t>71.77</t>
-        </is>
-      </c>
-      <c r="AX104" t="inlineStr">
-        <is>
-          <t>23.16</t>
-        </is>
-      </c>
-      <c r="AY104" t="inlineStr">
-        <is>
-          <t>32.72</t>
-        </is>
-      </c>
-      <c r="AZ104" t="inlineStr">
-        <is>
-          <t>22.36</t>
-        </is>
-      </c>
-      <c r="BA104" t="inlineStr">
-        <is>
-          <t>10.8</t>
-        </is>
-      </c>
-      <c r="BB104" t="inlineStr">
-        <is>
-          <t>0.1374</t>
-        </is>
-      </c>
-      <c r="BC104" t="inlineStr">
-        <is>
-          <t>6.96</t>
-        </is>
-      </c>
-      <c r="BD104" t="inlineStr">
-        <is>
-          <t>41.41</t>
-        </is>
-      </c>
-      <c r="BE104" t="inlineStr">
-        <is>
-          <t>89.14</t>
-        </is>
-      </c>
-      <c r="BF104" t="inlineStr">
-        <is>
-          <t>0.3548</t>
-        </is>
-      </c>
-      <c r="BG104" t="inlineStr">
-        <is>
-          <t>0.1228</t>
-        </is>
-      </c>
-      <c r="BH104" t="inlineStr">
-        <is>
-          <t>16.9</t>
-        </is>
-      </c>
-      <c r="BI104" t="inlineStr">
-        <is>
-          <t>106 deg</t>
-        </is>
-      </c>
-      <c r="BJ104" t="inlineStr">
-        <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
-        </is>
-      </c>
-      <c r="BK104" t="inlineStr">
-        <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=39.9061&amp;lon=-75.1665</t>
-        </is>
-      </c>
-      <c r="BL104" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="BM104" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="BN104" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BO104" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BP104" t="inlineStr"/>
@@ -34115,47 +34115,47 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>691026</t>
+          <t>672640</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Masyn Winn</t>
+          <t>Otto Lopez</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-08-17T17:40:00Z</t>
+          <t>2026-08-17T22:40:00Z</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Kent Emanuel</t>
+          <t>Cristopher Sánchez</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>592288</t>
+          <t>650911</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -34164,7 +34164,7 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>45.3</v>
+        <v>45.5</v>
       </c>
       <c r="M105" t="inlineStr">
         <is>
@@ -34178,26 +34178,26 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>Good Environment, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P105" t="n">
-        <v>15.7</v>
+        <v>29.8</v>
       </c>
       <c r="Q105" t="n">
-        <v>41.2</v>
+        <v>32.1</v>
       </c>
       <c r="R105" t="n">
-        <v>78.3</v>
+        <v>52.8</v>
       </c>
       <c r="S105" t="n">
-        <v>76.2</v>
+        <v>88.7</v>
       </c>
       <c r="T105" t="n">
         <v>78</v>
       </c>
       <c r="U105" t="n">
-        <v>10.8</v>
+        <v>7</v>
       </c>
       <c r="V105" t="n">
         <v>50</v>
@@ -34205,42 +34205,42 @@
       <c r="W105" t="inlineStr"/>
       <c r="X105" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y105" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA105" t="inlineStr">
+      <c r="AB105" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
         </is>
       </c>
       <c r="AD105" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
+          <t>lineup projected / unconfirmed</t>
         </is>
       </c>
       <c r="AE105" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF105" t="inlineStr"/>
@@ -34262,7 +34262,7 @@
       </c>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AL105" t="inlineStr">
@@ -34272,12 +34272,12 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 0 HR</t>
+          <t>Last 7 games: 5/30, 0 HR</t>
         </is>
       </c>
       <c r="AN105" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.0% barrel, 12.7 HR allowed</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
@@ -34287,78 +34287,102 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AQ105" t="inlineStr">
         <is>
-          <t>34.95</t>
+          <t>40.26</t>
         </is>
       </c>
       <c r="AR105" t="inlineStr">
         <is>
-          <t>88.23</t>
+          <t>88.85</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr">
         <is>
-          <t>98.6673</t>
+          <t>100.178</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr">
         <is>
-          <t>0.3372</t>
+          <t>0.4228</t>
         </is>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>0.0895</t>
+          <t>0.1461</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>0.2972</t>
+          <t>0.3237</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>71.17</t>
+          <t>71.77</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>15.77</t>
+          <t>23.16</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>32.11</t>
+          <t>32.72</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>21.32</t>
+          <t>22.36</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>0.089</t>
-        </is>
-      </c>
-      <c r="BC105" t="inlineStr"/>
-      <c r="BD105" t="inlineStr"/>
-      <c r="BE105" t="inlineStr"/>
-      <c r="BF105" t="inlineStr"/>
-      <c r="BG105" t="inlineStr"/>
-      <c r="BH105" t="inlineStr"/>
+          <t>0.1374</t>
+        </is>
+      </c>
+      <c r="BC105" t="inlineStr">
+        <is>
+          <t>6.96</t>
+        </is>
+      </c>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>41.41</t>
+        </is>
+      </c>
+      <c r="BE105" t="inlineStr">
+        <is>
+          <t>89.14</t>
+        </is>
+      </c>
+      <c r="BF105" t="inlineStr">
+        <is>
+          <t>0.3548</t>
+        </is>
+      </c>
+      <c r="BG105" t="inlineStr">
+        <is>
+          <t>0.1228</t>
+        </is>
+      </c>
+      <c r="BH105" t="inlineStr">
+        <is>
+          <t>16.9</t>
+        </is>
+      </c>
       <c r="BI105" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>106 deg</t>
         </is>
       </c>
       <c r="BJ105" t="inlineStr">
@@ -34368,27 +34392,27 @@
       </c>
       <c r="BK105" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=39.0979&amp;lon=-84.5082</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=39.9061&amp;lon=-75.1665</t>
         </is>
       </c>
       <c r="BL105" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM105" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="BN105" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BO105" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BP105" t="inlineStr"/>
@@ -34409,47 +34433,47 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>687637</t>
+          <t>691026</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Dylan Beavers</t>
+          <t>Masyn Winn</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-08-17T22:05:00Z</t>
+          <t>2026-08-17T17:40:00Z</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Shane McClanahan</t>
+          <t>Kent Emanuel</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>663556</t>
+          <t>592288</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -34472,26 +34496,26 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P106" t="n">
-        <v>29.2</v>
+        <v>15.7</v>
       </c>
       <c r="Q106" t="n">
         <v>41.2</v>
       </c>
       <c r="R106" t="n">
-        <v>53.1</v>
+        <v>78.3</v>
       </c>
       <c r="S106" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T106" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U106" t="n">
-        <v>26.4</v>
+        <v>10.8</v>
       </c>
       <c r="V106" t="n">
         <v>50</v>
@@ -34499,17 +34523,17 @@
       <c r="W106" t="inlineStr"/>
       <c r="X106" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y106" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -34524,17 +34548,17 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD106" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 7</t>
         </is>
       </c>
       <c r="AE106" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AF106" t="inlineStr"/>
@@ -34551,27 +34575,27 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AL106" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/23, 1 HR</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AN106" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.6% barrel, 7.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
@@ -34581,102 +34605,78 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="AQ106" t="inlineStr">
         <is>
-          <t>36.47</t>
+          <t>34.95</t>
         </is>
       </c>
       <c r="AR106" t="inlineStr">
         <is>
-          <t>88.87</t>
+          <t>88.23</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr">
         <is>
-          <t>99.3636</t>
+          <t>98.6673</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr">
         <is>
-          <t>0.373</t>
+          <t>0.3372</t>
         </is>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>0.1467</t>
+          <t>0.0895</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>0.3118</t>
+          <t>0.2972</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>72.34</t>
+          <t>71.17</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>20.49</t>
+          <t>15.77</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>32.11</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>31.04</t>
+          <t>21.32</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>0.1233</t>
-        </is>
-      </c>
-      <c r="BC106" t="inlineStr">
-        <is>
-          <t>8.6</t>
-        </is>
-      </c>
-      <c r="BD106" t="inlineStr">
-        <is>
-          <t>40.3</t>
-        </is>
-      </c>
-      <c r="BE106" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="BF106" t="inlineStr">
-        <is>
-          <t>0.399</t>
-        </is>
-      </c>
-      <c r="BG106" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
-      <c r="BH106" t="inlineStr">
-        <is>
-          <t>27.3</t>
-        </is>
-      </c>
+          <t>0.089</t>
+        </is>
+      </c>
+      <c r="BC106" t="inlineStr"/>
+      <c r="BD106" t="inlineStr"/>
+      <c r="BE106" t="inlineStr"/>
+      <c r="BF106" t="inlineStr"/>
+      <c r="BG106" t="inlineStr"/>
+      <c r="BH106" t="inlineStr"/>
       <c r="BI106" t="inlineStr">
         <is>
-          <t>286 deg</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ106" t="inlineStr">
@@ -34686,27 +34686,27 @@
       </c>
       <c r="BK106" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=27.7682&amp;lon=-82.6534</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=39.0979&amp;lon=-84.5082</t>
         </is>
       </c>
       <c r="BL106" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BM106" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="BN106" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BO106" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BP106" t="inlineStr"/>
@@ -34727,27 +34727,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>678882</t>
+          <t>687637</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Ceddanne Rafaela</t>
+          <t>Dylan Beavers</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-08-17T23:10:00Z</t>
+          <t>2026-08-17T22:05:00Z</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -34757,17 +34757,17 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Mitch Bratt</t>
+          <t>Shane McClanahan</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>683352</t>
+          <t>663556</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -34776,7 +34776,7 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>45.1</v>
+        <v>45.3</v>
       </c>
       <c r="M107" t="inlineStr">
         <is>
@@ -34790,26 +34790,26 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P107" t="n">
-        <v>22.5</v>
+        <v>29.2</v>
       </c>
       <c r="Q107" t="n">
-        <v>29.8</v>
+        <v>41.2</v>
       </c>
       <c r="R107" t="n">
-        <v>52.2</v>
+        <v>53.1</v>
       </c>
       <c r="S107" t="n">
-        <v>95.5</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T107" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U107" t="n">
-        <v>36.5</v>
+        <v>26.4</v>
       </c>
       <c r="V107" t="n">
         <v>50</v>
@@ -34827,7 +34827,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -34869,12 +34869,12 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AL107" t="inlineStr">
@@ -34884,117 +34884,117 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/29, 1 HR</t>
+          <t>Last 7 games: 4/23, 1 HR</t>
         </is>
       </c>
       <c r="AN107" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 5.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.6% barrel, 7.0 HR allowed</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>6.61</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="AQ107" t="inlineStr">
         <is>
-          <t>34.36</t>
+          <t>36.47</t>
         </is>
       </c>
       <c r="AR107" t="inlineStr">
         <is>
-          <t>86.97</t>
+          <t>88.87</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr">
         <is>
-          <t>97.8335</t>
+          <t>99.3636</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr">
         <is>
-          <t>0.3775</t>
+          <t>0.373</t>
         </is>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.1467</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>0.3118</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>70.02</t>
+          <t>72.34</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>8.83</t>
+          <t>20.49</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>35.78</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>25.65</t>
+          <t>31.04</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>0.1741</t>
+          <t>0.1233</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="BD107" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="BE107" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="BF107" t="inlineStr">
         <is>
-          <t>0.351</t>
+          <t>0.399</t>
         </is>
       </c>
       <c r="BG107" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="BH107" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="BI107" t="inlineStr">
         <is>
-          <t>186 deg</t>
+          <t>286 deg</t>
         </is>
       </c>
       <c r="BJ107" t="inlineStr">
@@ -35004,27 +35004,27 @@
       </c>
       <c r="BK107" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=42.3467&amp;lon=-71.0972</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=27.7682&amp;lon=-82.6534</t>
         </is>
       </c>
       <c r="BL107" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BN107" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BO107" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BP107" t="inlineStr"/>
@@ -35045,27 +35045,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>650402</t>
+          <t>678882</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Gleyber Torres</t>
+          <t>Ceddanne Rafaela</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-08-17T23:05:00Z</t>
+          <t>2026-08-17T23:10:00Z</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -35075,26 +35075,26 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Carmen Mlodzinski</t>
+          <t>Mitch Bratt</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>669387</t>
+          <t>683352</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L108" t="n">
-        <v>45</v>
+        <v>45.1</v>
       </c>
       <c r="M108" t="inlineStr">
         <is>
@@ -35108,26 +35108,26 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P108" t="n">
-        <v>25.9</v>
+        <v>22.5</v>
       </c>
       <c r="Q108" t="n">
-        <v>41.1</v>
+        <v>29.8</v>
       </c>
       <c r="R108" t="n">
-        <v>42.8</v>
+        <v>52.2</v>
       </c>
       <c r="S108" t="n">
-        <v>88.7</v>
+        <v>95.5</v>
       </c>
       <c r="T108" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U108" t="n">
-        <v>52.1</v>
+        <v>36.5</v>
       </c>
       <c r="V108" t="n">
         <v>50</v>
@@ -35145,7 +35145,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -35170,7 +35170,7 @@
       </c>
       <c r="AE108" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF108" t="inlineStr"/>
@@ -35187,7 +35187,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -35202,117 +35202,117 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>Contact streak: 10/29 over last 7 games</t>
+          <t>Last 7 games: 7/29, 1 HR</t>
         </is>
       </c>
       <c r="AN108" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 8.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 5.0 HR allowed</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>6.61</t>
         </is>
       </c>
       <c r="AQ108" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>34.36</t>
         </is>
       </c>
       <c r="AR108" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>86.97</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr">
         <is>
-          <t>97.7198</t>
+          <t>97.8335</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>0.3775</t>
         </is>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>0.1496</t>
+          <t>0.132</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>0.342</t>
+          <t>0.291</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>68.63</t>
+          <t>70.02</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>5.82</t>
+          <t>8.83</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>26.41</t>
+          <t>35.78</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>27.66</t>
+          <t>25.65</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>10.4</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>0.1338</t>
+          <t>0.1741</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BD108" t="inlineStr">
         <is>
-          <t>45.35</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BE108" t="inlineStr">
         <is>
-          <t>90.62</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="BF108" t="inlineStr">
         <is>
-          <t>0.4251</t>
+          <t>0.351</t>
         </is>
       </c>
       <c r="BG108" t="inlineStr">
         <is>
-          <t>0.1441</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="BH108" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>33.7</t>
         </is>
       </c>
       <c r="BI108" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>186 deg</t>
         </is>
       </c>
       <c r="BJ108" t="inlineStr">
@@ -35322,27 +35322,27 @@
       </c>
       <c r="BK108" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=40.4469&amp;lon=-80.0057</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=42.3467&amp;lon=-71.0972</t>
         </is>
       </c>
       <c r="BL108" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>52</t>
         </is>
       </c>
       <c r="BM108" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN108" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BO108" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BP108" t="inlineStr"/>
@@ -35363,27 +35363,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>702616</t>
+          <t>650402</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Jackson Holliday</t>
+          <t>Gleyber Torres</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-08-17T22:05:00Z</t>
+          <t>2026-08-17T23:05:00Z</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -35393,26 +35393,26 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Shane McClanahan</t>
+          <t>Carmen Mlodzinski</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>663556</t>
+          <t>669387</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>44.8</v>
+        <v>45</v>
       </c>
       <c r="M109" t="inlineStr">
         <is>
@@ -35430,29 +35430,27 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>27.4</v>
+        <v>25.9</v>
       </c>
       <c r="Q109" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="R109" t="n">
-        <v>53.1</v>
+        <v>42.8</v>
       </c>
       <c r="S109" t="n">
-        <v>92.09999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="T109" t="n">
         <v>50</v>
       </c>
       <c r="U109" t="n">
-        <v>22</v>
+        <v>52.1</v>
       </c>
       <c r="V109" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="W109" t="n">
-        <v>55</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="W109" t="inlineStr"/>
       <c r="X109" t="inlineStr">
         <is>
           <t>No</t>
@@ -35465,7 +35463,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -35490,7 +35488,7 @@
       </c>
       <c r="AE109" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF109" t="inlineStr"/>
@@ -35507,27 +35505,27 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/30, 0 HR</t>
+          <t>Contact streak: 10/29 over last 7 games</t>
         </is>
       </c>
       <c r="AN109" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.6% barrel, 7.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
@@ -35537,102 +35535,102 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>7.8</t>
+          <t>7.43</t>
         </is>
       </c>
       <c r="AQ109" t="inlineStr">
         <is>
-          <t>36.95</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="AR109" t="inlineStr">
         <is>
-          <t>87.82</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr">
         <is>
-          <t>98.1913</t>
+          <t>97.7198</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr">
         <is>
-          <t>0.3809</t>
+          <t>0.406</t>
         </is>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>0.1406</t>
+          <t>0.1496</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>0.3168</t>
+          <t>0.342</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>68.63</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>5.82</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>36.25</t>
+          <t>26.41</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>24.89</t>
+          <t>27.66</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>0.1379</t>
+          <t>0.1338</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="BD109" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="BE109" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>90.62</t>
         </is>
       </c>
       <c r="BF109" t="inlineStr">
         <is>
-          <t>0.399</t>
+          <t>0.4251</t>
         </is>
       </c>
       <c r="BG109" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.1441</t>
         </is>
       </c>
       <c r="BH109" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="BI109" t="inlineStr">
         <is>
-          <t>286 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ109" t="inlineStr">
@@ -35642,80 +35640,40 @@
       </c>
       <c r="BK109" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=27.7682&amp;lon=-82.6534</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=40.4469&amp;lon=-80.0057</t>
         </is>
       </c>
       <c r="BL109" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BM109" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>28</t>
         </is>
       </c>
       <c r="BN109" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO109" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BP109" t="inlineStr"/>
-      <c r="BQ109" t="inlineStr">
-        <is>
-          <t>13.0</t>
-        </is>
-      </c>
-      <c r="BR109" t="inlineStr">
-        <is>
-          <t>0.227</t>
-        </is>
-      </c>
-      <c r="BS109" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="BT109" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BU109" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="BV109" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW109" t="inlineStr">
-        <is>
-          <t>-4</t>
-        </is>
-      </c>
-      <c r="BX109" t="inlineStr">
-        <is>
-          <t>5.43</t>
-        </is>
-      </c>
-      <c r="BY109" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BZ109" t="inlineStr">
-        <is>
-          <t>Best BAL full sheet line but park neutral-negative</t>
-        </is>
-      </c>
+      <c r="BQ109" t="inlineStr"/>
+      <c r="BR109" t="inlineStr"/>
+      <c r="BS109" t="inlineStr"/>
+      <c r="BT109" t="inlineStr"/>
+      <c r="BU109" t="inlineStr"/>
+      <c r="BV109" t="inlineStr"/>
+      <c r="BW109" t="inlineStr"/>
+      <c r="BX109" t="inlineStr"/>
+      <c r="BY109" t="inlineStr"/>
+      <c r="BZ109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -35723,27 +35681,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>605170</t>
+          <t>702616</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Victor Caratini</t>
+          <t>Jackson Holliday</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
           <t>MIN</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-08-17T23:40:00Z</t>
+          <t>2026-08-17T22:05:00Z</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -35753,17 +35711,17 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Martín Pérez</t>
+          <t>Shane McClanahan</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>527048</t>
+          <t>663556</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -35786,31 +35744,33 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P110" t="n">
-        <v>31</v>
+        <v>27.4</v>
       </c>
       <c r="Q110" t="n">
-        <v>37.9</v>
+        <v>41.2</v>
       </c>
       <c r="R110" t="n">
-        <v>52.6</v>
+        <v>53.1</v>
       </c>
       <c r="S110" t="n">
-        <v>71.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T110" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U110" t="n">
-        <v>10.6</v>
+        <v>22</v>
       </c>
       <c r="V110" t="n">
-        <v>50</v>
-      </c>
-      <c r="W110" t="inlineStr"/>
+        <v>28.9</v>
+      </c>
+      <c r="W110" t="n">
+        <v>55</v>
+      </c>
       <c r="X110" t="inlineStr">
         <is>
           <t>No</t>
@@ -35823,7 +35783,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -35848,7 +35808,7 @@
       </c>
       <c r="AE110" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF110" t="inlineStr"/>
@@ -35865,175 +35825,215 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AL110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>Last 7 games: 8/30, 0 HR</t>
+        </is>
+      </c>
+      <c r="AN110" t="inlineStr">
+        <is>
+          <t>same-side matchup; pitcher baseline 8.6% barrel, 7.0 HR allowed</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+        </is>
+      </c>
+      <c r="AP110" t="inlineStr">
+        <is>
+          <t>7.8</t>
+        </is>
+      </c>
+      <c r="AQ110" t="inlineStr">
+        <is>
+          <t>36.95</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>87.82</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr">
+        <is>
+          <t>98.1913</t>
+        </is>
+      </c>
+      <c r="AT110" t="inlineStr">
+        <is>
+          <t>0.3809</t>
+        </is>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>0.1406</t>
+        </is>
+      </c>
+      <c r="AV110" t="inlineStr">
+        <is>
+          <t>0.3168</t>
+        </is>
+      </c>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>70.6</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>7.27</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t>36.25</t>
+        </is>
+      </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>24.89</t>
+        </is>
+      </c>
+      <c r="BA110" t="inlineStr">
+        <is>
+          <t>9.3</t>
+        </is>
+      </c>
+      <c r="BB110" t="inlineStr">
+        <is>
+          <t>0.1379</t>
+        </is>
+      </c>
+      <c r="BC110" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
+      </c>
+      <c r="BD110" t="inlineStr">
+        <is>
+          <t>40.3</t>
+        </is>
+      </c>
+      <c r="BE110" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="BF110" t="inlineStr">
+        <is>
+          <t>0.399</t>
+        </is>
+      </c>
+      <c r="BG110" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="BH110" t="inlineStr">
+        <is>
+          <t>27.3</t>
+        </is>
+      </c>
+      <c r="BI110" t="inlineStr">
+        <is>
+          <t>286 deg</t>
+        </is>
+      </c>
+      <c r="BJ110" t="inlineStr">
+        <is>
+          <t>Open-Meteo forecast; MLB fallback</t>
+        </is>
+      </c>
+      <c r="BK110" t="inlineStr">
+        <is>
+          <t>https://forecast.weather.gov/MapClick.php?lat=27.7682&amp;lon=-82.6534</t>
+        </is>
+      </c>
+      <c r="BL110" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="BM110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BN110" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="BO110" t="inlineStr">
+        <is>
+          <t>Tropicana Field</t>
+        </is>
+      </c>
+      <c r="BP110" t="inlineStr"/>
+      <c r="BQ110" t="inlineStr">
+        <is>
+          <t>13.0</t>
+        </is>
+      </c>
+      <c r="BR110" t="inlineStr">
+        <is>
+          <t>0.227</t>
+        </is>
+      </c>
+      <c r="BS110" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="BT110" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AL110" t="inlineStr">
+      <c r="BU110" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="BV110" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>Last 7 games: 4/21, 0 HR</t>
-        </is>
-      </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>switch hitter; pitcher baseline 8.4% barrel, 9.5 HR allowed</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
-        </is>
-      </c>
-      <c r="AP110" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AQ110" t="inlineStr">
-        <is>
-          <t>39.86</t>
-        </is>
-      </c>
-      <c r="AR110" t="inlineStr">
-        <is>
-          <t>89.33</t>
-        </is>
-      </c>
-      <c r="AS110" t="inlineStr">
-        <is>
-          <t>99.0024</t>
-        </is>
-      </c>
-      <c r="AT110" t="inlineStr">
-        <is>
-          <t>0.3963</t>
-        </is>
-      </c>
-      <c r="AU110" t="inlineStr">
-        <is>
-          <t>0.1539</t>
-        </is>
-      </c>
-      <c r="AV110" t="inlineStr">
-        <is>
-          <t>0.3234</t>
-        </is>
-      </c>
-      <c r="AW110" t="inlineStr">
-        <is>
-          <t>71.39</t>
-        </is>
-      </c>
-      <c r="AX110" t="inlineStr">
-        <is>
-          <t>16.29</t>
-        </is>
-      </c>
-      <c r="AY110" t="inlineStr">
-        <is>
-          <t>37.43</t>
-        </is>
-      </c>
-      <c r="AZ110" t="inlineStr">
-        <is>
-          <t>24.04</t>
-        </is>
-      </c>
-      <c r="BA110" t="inlineStr">
-        <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="BB110" t="inlineStr">
-        <is>
-          <t>0.1177</t>
-        </is>
-      </c>
-      <c r="BC110" t="inlineStr">
-        <is>
-          <t>8.42</t>
-        </is>
-      </c>
-      <c r="BD110" t="inlineStr">
-        <is>
-          <t>38.0</t>
-        </is>
-      </c>
-      <c r="BE110" t="inlineStr">
-        <is>
-          <t>88.2</t>
-        </is>
-      </c>
-      <c r="BF110" t="inlineStr">
-        <is>
-          <t>0.4157</t>
-        </is>
-      </c>
-      <c r="BG110" t="inlineStr">
-        <is>
-          <t>0.1639</t>
-        </is>
-      </c>
-      <c r="BH110" t="inlineStr">
-        <is>
-          <t>24.27</t>
-        </is>
-      </c>
-      <c r="BI110" t="inlineStr">
-        <is>
-          <t>330 deg</t>
-        </is>
-      </c>
-      <c r="BJ110" t="inlineStr">
-        <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
-        </is>
-      </c>
-      <c r="BK110" t="inlineStr">
-        <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
-        </is>
-      </c>
-      <c r="BL110" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="BM110" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN110" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="BO110" t="inlineStr">
-        <is>
-          <t>Target Field</t>
-        </is>
-      </c>
-      <c r="BP110" t="inlineStr"/>
-      <c r="BQ110" t="inlineStr"/>
-      <c r="BR110" t="inlineStr"/>
-      <c r="BS110" t="inlineStr"/>
-      <c r="BT110" t="inlineStr"/>
-      <c r="BU110" t="inlineStr"/>
-      <c r="BV110" t="inlineStr"/>
-      <c r="BW110" t="inlineStr"/>
-      <c r="BX110" t="inlineStr"/>
-      <c r="BY110" t="inlineStr"/>
-      <c r="BZ110" t="inlineStr"/>
+      <c r="BW110" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="BX110" t="inlineStr">
+        <is>
+          <t>5.43</t>
+        </is>
+      </c>
+      <c r="BY110" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BZ110" t="inlineStr">
+        <is>
+          <t>Best BAL full sheet line but park neutral-negative</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -39781,47 +39781,47 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>668885</t>
+          <t>680574</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Austin Martin</t>
+          <t>Matt McLain</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-08-17T23:40:00Z</t>
+          <t>2026-08-17T17:40:00Z</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Martín Pérez</t>
+          <t>Quinn Mathews</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>527048</t>
+          <t>687273</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -39830,7 +39830,7 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>42.7</v>
+        <v>42.4</v>
       </c>
       <c r="M123" t="inlineStr">
         <is>
@@ -39844,26 +39844,26 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P123" t="n">
-        <v>12.2</v>
+        <v>33.7</v>
       </c>
       <c r="Q123" t="n">
-        <v>39</v>
+        <v>7.2</v>
       </c>
       <c r="R123" t="n">
-        <v>52.6</v>
+        <v>78.3</v>
       </c>
       <c r="S123" t="n">
-        <v>81.90000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T123" t="n">
         <v>78</v>
       </c>
       <c r="U123" t="n">
-        <v>47.7</v>
+        <v>31.6</v>
       </c>
       <c r="V123" t="n">
         <v>50</v>
@@ -39871,17 +39871,17 @@
       <c r="W123" t="inlineStr"/>
       <c r="X123" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y123" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -39896,17 +39896,17 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AD123" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 9</t>
         </is>
       </c>
       <c r="AE123" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF123" t="inlineStr"/>
@@ -39923,12 +39923,12 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL123" t="inlineStr">
@@ -39938,117 +39938,117 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/19, 1 HR</t>
+          <t>Last 7 games: 5/24, 1 HR</t>
         </is>
       </c>
       <c r="AN123" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 9.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="AQ123" t="inlineStr">
         <is>
-          <t>32.09</t>
+          <t>37.97</t>
         </is>
       </c>
       <c r="AR123" t="inlineStr">
         <is>
-          <t>86.76</t>
+          <t>88.24</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr">
         <is>
-          <t>97.3124</t>
+          <t>98.9599</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr">
         <is>
-          <t>0.3491</t>
+          <t>0.3799</t>
         </is>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>0.0974</t>
+          <t>0.1574</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>0.3212</t>
+          <t>0.3082</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>68.83</t>
+          <t>70.93</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>40.79</t>
+          <t>34.73</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>21.12</t>
+          <t>32.87</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>0.0893</t>
+          <t>0.1447</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>8.42</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BD123" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="BE123" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="BF123" t="inlineStr">
         <is>
-          <t>0.4157</t>
+          <t>0.288</t>
         </is>
       </c>
       <c r="BG123" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.041</t>
         </is>
       </c>
       <c r="BH123" t="inlineStr">
         <is>
-          <t>24.27</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="BI123" t="inlineStr">
         <is>
-          <t>330 deg</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ123" t="inlineStr">
@@ -40058,27 +40058,27 @@
       </c>
       <c r="BK123" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=39.0979&amp;lon=-84.5082</t>
         </is>
       </c>
       <c r="BL123" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BM123" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="BN123" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BO123" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BP123" t="inlineStr"/>
@@ -40119,12 +40119,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-08-17T17:40:00Z</t>
+          <t>2026-08-17T22:40:00Z</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -40134,21 +40134,21 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Quinn Mathews</t>
+          <t>Andre Pallante</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>687273</t>
+          <t>669467</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>42.4</v>
+        <v>42.2</v>
       </c>
       <c r="M124" t="inlineStr">
         <is>
@@ -40162,23 +40162,23 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>Good Environment, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P124" t="n">
         <v>33.7</v>
       </c>
       <c r="Q124" t="n">
-        <v>7.2</v>
+        <v>27.2</v>
       </c>
       <c r="R124" t="n">
-        <v>78.3</v>
+        <v>64.8</v>
       </c>
       <c r="S124" t="n">
-        <v>64.3</v>
+        <v>59.8</v>
       </c>
       <c r="T124" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U124" t="n">
         <v>31.6</v>
@@ -40189,42 +40189,42 @@
       <c r="W124" t="inlineStr"/>
       <c r="X124" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y124" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA124" t="inlineStr">
+      <c r="AB124" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC124" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
         </is>
       </c>
       <c r="AD124" t="inlineStr">
         <is>
-          <t>RotoWire not confirmed; order MLB 7 vs RotoWire 9</t>
+          <t>lineup projected / unconfirmed; order MLB 7 vs RotoWire 9</t>
         </is>
       </c>
       <c r="AE124" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF124" t="inlineStr"/>
@@ -40261,12 +40261,12 @@
       </c>
       <c r="AN124" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.8% barrel, 13.3 HR allowed</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
@@ -40336,37 +40336,37 @@
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="BD124" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>36.26</t>
         </is>
       </c>
       <c r="BE124" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>88.01</t>
         </is>
       </c>
       <c r="BF124" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>0.3817</t>
         </is>
       </c>
       <c r="BG124" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>0.1321</t>
         </is>
       </c>
       <c r="BH124" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>17.68</t>
         </is>
       </c>
       <c r="BI124" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>288 deg</t>
         </is>
       </c>
       <c r="BJ124" t="inlineStr">
@@ -40417,27 +40417,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>680574</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Matt McLain</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-08-17T22:40:00Z</t>
+          <t>2026-08-17T22:05:00Z</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -40447,17 +40447,17 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Andre Pallante</t>
+          <t>Brandon Young</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>669467</t>
+          <t>687064</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -40480,26 +40480,26 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P125" t="n">
-        <v>33.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q125" t="n">
-        <v>27.2</v>
+        <v>40.3</v>
       </c>
       <c r="R125" t="n">
-        <v>64.8</v>
+        <v>53.1</v>
       </c>
       <c r="S125" t="n">
-        <v>59.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T125" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U125" t="n">
-        <v>31.6</v>
+        <v>47.7</v>
       </c>
       <c r="V125" t="n">
         <v>50</v>
@@ -40517,7 +40517,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -40537,7 +40537,7 @@
       </c>
       <c r="AD125" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed; order MLB 7 vs RotoWire 9</t>
+          <t>lineup projected / unconfirmed</t>
         </is>
       </c>
       <c r="AE125" t="inlineStr">
@@ -40559,12 +40559,12 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AL125" t="inlineStr">
@@ -40574,12 +40574,12 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 1 HR</t>
+          <t>Last 7 games: 6/19, 1 HR</t>
         </is>
       </c>
       <c r="AN125" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.8% barrel, 13.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.3% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
@@ -40589,102 +40589,102 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="AQ125" t="inlineStr">
         <is>
-          <t>37.97</t>
+          <t>28.12</t>
         </is>
       </c>
       <c r="AR125" t="inlineStr">
         <is>
-          <t>88.24</t>
+          <t>84.81</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr">
         <is>
-          <t>98.9599</t>
+          <t>96.2382</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr">
         <is>
-          <t>0.3799</t>
+          <t>0.3521</t>
         </is>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>0.1574</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>0.3082</t>
+          <t>0.3171</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>70.93</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>3.93</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>34.73</t>
+          <t>42.38</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>32.87</t>
+          <t>24.57</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>0.1447</t>
+          <t>0.1424</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>5.83</t>
+          <t>7.33</t>
         </is>
       </c>
       <c r="BD125" t="inlineStr">
         <is>
-          <t>36.26</t>
+          <t>41.36</t>
         </is>
       </c>
       <c r="BE125" t="inlineStr">
         <is>
-          <t>88.01</t>
+          <t>89.33</t>
         </is>
       </c>
       <c r="BF125" t="inlineStr">
         <is>
-          <t>0.3817</t>
+          <t>0.4082</t>
         </is>
       </c>
       <c r="BG125" t="inlineStr">
         <is>
-          <t>0.1321</t>
+          <t>0.1588</t>
         </is>
       </c>
       <c r="BH125" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>27.15</t>
         </is>
       </c>
       <c r="BI125" t="inlineStr">
         <is>
-          <t>288 deg</t>
+          <t>286 deg</t>
         </is>
       </c>
       <c r="BJ125" t="inlineStr">
@@ -40694,27 +40694,27 @@
       </c>
       <c r="BK125" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=39.0979&amp;lon=-84.5082</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=27.7682&amp;lon=-82.6534</t>
         </is>
       </c>
       <c r="BL125" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BM125" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BN125" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BO125" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BP125" t="inlineStr"/>
@@ -40735,27 +40735,27 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>686797</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Brooks Lee</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-08-17T22:05:00Z</t>
+          <t>2026-08-17T23:40:00Z</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -40765,26 +40765,26 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Brandon Young</t>
+          <t>Martín Pérez</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>687064</t>
+          <t>527048</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="M126" t="inlineStr">
         <is>
@@ -40798,26 +40798,26 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P126" t="n">
-        <v>8.800000000000001</v>
+        <v>18.3</v>
       </c>
       <c r="Q126" t="n">
-        <v>40.3</v>
+        <v>37.9</v>
       </c>
       <c r="R126" t="n">
-        <v>53.1</v>
+        <v>52.6</v>
       </c>
       <c r="S126" t="n">
-        <v>81.90000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T126" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U126" t="n">
-        <v>47.7</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="V126" t="n">
         <v>50</v>
@@ -40835,7 +40835,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -40877,27 +40877,27 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL126" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/19, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN126" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.3% barrel, 12.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.4% barrel, 9.5 HR allowed</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
@@ -40907,102 +40907,102 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>3.88</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="AQ126" t="inlineStr">
         <is>
-          <t>28.12</t>
+          <t>33.88</t>
         </is>
       </c>
       <c r="AR126" t="inlineStr">
         <is>
-          <t>84.81</t>
+          <t>87.97</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr">
         <is>
-          <t>96.2382</t>
+          <t>97.4055</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr">
         <is>
-          <t>0.3521</t>
+          <t>0.3411</t>
         </is>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.1155</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>0.3171</t>
+          <t>0.275</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>69.92</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>3.93</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>42.38</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>24.57</t>
+          <t>28.09</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>0.1424</t>
+          <t>0.1655</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>7.33</t>
+          <t>8.42</t>
         </is>
       </c>
       <c r="BD126" t="inlineStr">
         <is>
-          <t>41.36</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="BE126" t="inlineStr">
         <is>
-          <t>89.33</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="BF126" t="inlineStr">
         <is>
-          <t>0.4082</t>
+          <t>0.4157</t>
         </is>
       </c>
       <c r="BG126" t="inlineStr">
         <is>
-          <t>0.1588</t>
+          <t>0.1639</t>
         </is>
       </c>
       <c r="BH126" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>24.27</t>
         </is>
       </c>
       <c r="BI126" t="inlineStr">
         <is>
-          <t>286 deg</t>
+          <t>330 deg</t>
         </is>
       </c>
       <c r="BJ126" t="inlineStr">
@@ -41012,27 +41012,27 @@
       </c>
       <c r="BK126" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=27.7682&amp;lon=-82.6534</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
         </is>
       </c>
       <c r="BL126" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>43</t>
         </is>
       </c>
       <c r="BM126" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN126" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BO126" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BP126" t="inlineStr"/>
@@ -46427,27 +46427,27 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>686780</t>
+          <t>807712</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Pedro Pages</t>
+          <t>Luke Keaschall</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-08-17T22:40:00Z</t>
+          <t>2026-08-17T23:40:00Z</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -46457,26 +46457,26 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Rhett Lowder</t>
+          <t>Martín Pérez</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>695076</t>
+          <t>527048</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>40.7</v>
+        <v>40.8</v>
       </c>
       <c r="M144" t="inlineStr">
         <is>
@@ -46490,26 +46490,26 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P144" t="n">
-        <v>22.4</v>
+        <v>11.5</v>
       </c>
       <c r="Q144" t="n">
-        <v>50.9</v>
+        <v>39</v>
       </c>
       <c r="R144" t="n">
-        <v>64.8</v>
+        <v>52.6</v>
       </c>
       <c r="S144" t="n">
-        <v>40.2</v>
+        <v>71.7</v>
       </c>
       <c r="T144" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U144" t="n">
-        <v>16.6</v>
+        <v>43.2</v>
       </c>
       <c r="V144" t="n">
         <v>50</v>
@@ -46522,24 +46522,24 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA144" t="inlineStr">
+      <c r="AB144" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC144" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -46552,7 +46552,7 @@
       </c>
       <c r="AE144" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF144" t="inlineStr"/>
@@ -46569,162 +46569,162 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL144" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM144" t="inlineStr">
+        <is>
+          <t>Last 7 games: 6/21, 1 HR</t>
+        </is>
+      </c>
+      <c r="AN144" t="inlineStr">
+        <is>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 9.5 HR allowed</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+        </is>
+      </c>
+      <c r="AP144" t="inlineStr">
+        <is>
+          <t>3.73</t>
+        </is>
+      </c>
+      <c r="AQ144" t="inlineStr">
+        <is>
+          <t>29.87</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>85.29</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr">
+        <is>
+          <t>96.7373</t>
+        </is>
+      </c>
+      <c r="AT144" t="inlineStr">
+        <is>
+          <t>0.357</t>
+        </is>
+      </c>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>0.1104</t>
+        </is>
+      </c>
+      <c r="AV144" t="inlineStr">
+        <is>
+          <t>0.3149</t>
+        </is>
+      </c>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>68.64</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>7.73</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr">
+        <is>
+          <t>38.96</t>
+        </is>
+      </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>26.69</t>
+        </is>
+      </c>
+      <c r="BA144" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="BB144" t="inlineStr">
+        <is>
+          <t>0.1171</t>
+        </is>
+      </c>
+      <c r="BC144" t="inlineStr">
+        <is>
+          <t>8.42</t>
+        </is>
+      </c>
+      <c r="BD144" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
+      </c>
+      <c r="BE144" t="inlineStr">
+        <is>
+          <t>88.2</t>
+        </is>
+      </c>
+      <c r="BF144" t="inlineStr">
+        <is>
+          <t>0.4157</t>
+        </is>
+      </c>
+      <c r="BG144" t="inlineStr">
+        <is>
+          <t>0.1639</t>
+        </is>
+      </c>
+      <c r="BH144" t="inlineStr">
+        <is>
+          <t>24.27</t>
+        </is>
+      </c>
+      <c r="BI144" t="inlineStr">
+        <is>
+          <t>330 deg</t>
+        </is>
+      </c>
+      <c r="BJ144" t="inlineStr">
+        <is>
+          <t>Open-Meteo forecast; MLB fallback</t>
+        </is>
+      </c>
+      <c r="BK144" t="inlineStr">
+        <is>
+          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
+        </is>
+      </c>
+      <c r="BL144" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="BM144" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AM144" t="inlineStr">
-        <is>
-          <t>Last 7 games: 3/13, 0 HR</t>
-        </is>
-      </c>
-      <c r="AN144" t="inlineStr">
-        <is>
-          <t>same-side matchup; pitcher baseline 9.6% barrel, 12.0 HR allowed</t>
-        </is>
-      </c>
-      <c r="AO144" t="inlineStr">
-        <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
-        </is>
-      </c>
-      <c r="AP144" t="inlineStr">
-        <is>
-          <t>5.72</t>
-        </is>
-      </c>
-      <c r="AQ144" t="inlineStr">
-        <is>
-          <t>37.2</t>
-        </is>
-      </c>
-      <c r="AR144" t="inlineStr">
-        <is>
-          <t>86.95</t>
-        </is>
-      </c>
-      <c r="AS144" t="inlineStr">
-        <is>
-          <t>99.3673</t>
-        </is>
-      </c>
-      <c r="AT144" t="inlineStr">
-        <is>
-          <t>0.3379</t>
-        </is>
-      </c>
-      <c r="AU144" t="inlineStr">
-        <is>
-          <t>0.1236</t>
-        </is>
-      </c>
-      <c r="AV144" t="inlineStr">
-        <is>
-          <t>0.2639</t>
-        </is>
-      </c>
-      <c r="AW144" t="inlineStr">
-        <is>
-          <t>72.6</t>
-        </is>
-      </c>
-      <c r="AX144" t="inlineStr">
-        <is>
-          <t>24.22</t>
-        </is>
-      </c>
-      <c r="AY144" t="inlineStr">
-        <is>
-          <t>36.41</t>
-        </is>
-      </c>
-      <c r="AZ144" t="inlineStr">
-        <is>
-          <t>26.85</t>
-        </is>
-      </c>
-      <c r="BA144" t="inlineStr">
-        <is>
-          <t>6.1</t>
-        </is>
-      </c>
-      <c r="BB144" t="inlineStr">
-        <is>
-          <t>0.1176</t>
-        </is>
-      </c>
-      <c r="BC144" t="inlineStr">
-        <is>
-          <t>9.6</t>
-        </is>
-      </c>
-      <c r="BD144" t="inlineStr">
-        <is>
-          <t>38.2</t>
-        </is>
-      </c>
-      <c r="BE144" t="inlineStr">
-        <is>
-          <t>90.5</t>
-        </is>
-      </c>
-      <c r="BF144" t="inlineStr">
-        <is>
-          <t>0.456</t>
-        </is>
-      </c>
-      <c r="BG144" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
-      <c r="BH144" t="inlineStr">
-        <is>
-          <t>27.9</t>
-        </is>
-      </c>
-      <c r="BI144" t="inlineStr">
-        <is>
-          <t>288 deg</t>
-        </is>
-      </c>
-      <c r="BJ144" t="inlineStr">
-        <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
-        </is>
-      </c>
-      <c r="BK144" t="inlineStr">
-        <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=39.0979&amp;lon=-84.5082</t>
-        </is>
-      </c>
-      <c r="BL144" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="BM144" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="BN144" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BO144" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BP144" t="inlineStr"/>
@@ -46745,27 +46745,27 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>686555</t>
+          <t>686780</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Isaac Collins</t>
+          <t>Pedro Pages</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-08-17T23:40:00Z</t>
+          <t>2026-08-17T22:40:00Z</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -46775,17 +46775,17 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Mason Barnett</t>
+          <t>Rhett Lowder</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>686930</t>
+          <t>695076</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -46794,7 +46794,7 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>40.5</v>
+        <v>40.7</v>
       </c>
       <c r="M145" t="inlineStr">
         <is>
@@ -46808,26 +46808,26 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P145" t="n">
-        <v>23.4</v>
+        <v>22.4</v>
       </c>
       <c r="Q145" t="n">
-        <v>47.7</v>
+        <v>50.9</v>
       </c>
       <c r="R145" t="n">
-        <v>50.7</v>
+        <v>64.8</v>
       </c>
       <c r="S145" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T145" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U145" t="n">
-        <v>0</v>
+        <v>16.6</v>
       </c>
       <c r="V145" t="n">
         <v>50</v>
@@ -46840,12 +46840,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -46870,7 +46870,7 @@
       </c>
       <c r="AE145" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF145" t="inlineStr"/>
@@ -46887,12 +46887,12 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AL145" t="inlineStr">
@@ -46902,117 +46902,117 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/23, 0 HR</t>
+          <t>Last 7 games: 3/13, 0 HR</t>
         </is>
       </c>
       <c r="AN145" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 10.3% barrel, 8.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.6% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="AQ145" t="inlineStr">
         <is>
-          <t>39.53</t>
+          <t>37.2</t>
         </is>
       </c>
       <c r="AR145" t="inlineStr">
         <is>
-          <t>88.59</t>
+          <t>86.95</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr">
         <is>
-          <t>99.8845</t>
+          <t>99.3673</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr">
         <is>
-          <t>0.3345</t>
+          <t>0.3379</t>
         </is>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>0.1004</t>
+          <t>0.1236</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>0.3059</t>
+          <t>0.2639</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>24.22</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>36.41</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>26.23</t>
+          <t>26.85</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>0.1312</t>
+          <t>0.1176</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>10.31</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="BD145" t="inlineStr">
         <is>
-          <t>39.28</t>
+          <t>38.2</t>
         </is>
       </c>
       <c r="BE145" t="inlineStr">
         <is>
-          <t>88.78</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="BF145" t="inlineStr">
         <is>
-          <t>0.4158</t>
+          <t>0.456</t>
         </is>
       </c>
       <c r="BG145" t="inlineStr">
         <is>
-          <t>0.1796</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="BH145" t="inlineStr">
         <is>
-          <t>33.16</t>
+          <t>27.9</t>
         </is>
       </c>
       <c r="BI145" t="inlineStr">
         <is>
-          <t>354 deg</t>
+          <t>288 deg</t>
         </is>
       </c>
       <c r="BJ145" t="inlineStr">
@@ -47022,17 +47022,17 @@
       </c>
       <c r="BK145" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=39.0517&amp;lon=-94.4803</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=39.0979&amp;lon=-84.5082</t>
         </is>
       </c>
       <c r="BL145" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BM145" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="BN145" t="inlineStr">
@@ -47042,7 +47042,7 @@
       </c>
       <c r="BO145" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BP145" t="inlineStr"/>
@@ -47063,22 +47063,22 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>686797</t>
+          <t>686555</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Brooks Lee</t>
+          <t>Isaac Collins</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -47098,17 +47098,17 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Martín Pérez</t>
+          <t>Mason Barnett</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>527048</t>
+          <t>686930</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L146" t="n">
@@ -47126,17 +47126,17 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P146" t="n">
-        <v>18.3</v>
+        <v>23.4</v>
       </c>
       <c r="Q146" t="n">
-        <v>37.9</v>
+        <v>47.7</v>
       </c>
       <c r="R146" t="n">
-        <v>52.6</v>
+        <v>50.7</v>
       </c>
       <c r="S146" t="n">
         <v>47.9</v>
@@ -47145,7 +47145,7 @@
         <v>75</v>
       </c>
       <c r="U146" t="n">
-        <v>70.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="V146" t="n">
         <v>50</v>
@@ -47205,132 +47205,132 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AL146" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM146" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 2/23, 0 HR</t>
         </is>
       </c>
       <c r="AN146" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.4% barrel, 9.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 10.3% barrel, 8.6 HR allowed</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AQ146" t="inlineStr">
         <is>
-          <t>33.88</t>
+          <t>39.53</t>
         </is>
       </c>
       <c r="AR146" t="inlineStr">
         <is>
-          <t>87.97</t>
+          <t>88.59</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr">
         <is>
-          <t>97.4055</t>
+          <t>99.8845</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr">
         <is>
-          <t>0.3411</t>
+          <t>0.3345</t>
         </is>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>0.1155</t>
+          <t>0.1004</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>0.3059</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>69.92</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>28.09</t>
+          <t>26.23</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>0.1655</t>
+          <t>0.1312</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>8.42</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="BD146" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>39.28</t>
         </is>
       </c>
       <c r="BE146" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.78</t>
         </is>
       </c>
       <c r="BF146" t="inlineStr">
         <is>
-          <t>0.4157</t>
+          <t>0.4158</t>
         </is>
       </c>
       <c r="BG146" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.1796</t>
         </is>
       </c>
       <c r="BH146" t="inlineStr">
         <is>
-          <t>24.27</t>
+          <t>33.16</t>
         </is>
       </c>
       <c r="BI146" t="inlineStr">
         <is>
-          <t>330 deg</t>
+          <t>354 deg</t>
         </is>
       </c>
       <c r="BJ146" t="inlineStr">
@@ -47340,27 +47340,27 @@
       </c>
       <c r="BK146" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=39.0517&amp;lon=-94.4803</t>
         </is>
       </c>
       <c r="BL146" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BM146" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="BN146" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BO146" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BP146" t="inlineStr"/>
@@ -48335,27 +48335,27 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>650489</t>
+          <t>668952</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Willi Castro</t>
+          <t>Ryan Kreidler</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-08-18T00:40:00Z</t>
+          <t>2026-08-17T23:40:00Z</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -48365,17 +48365,17 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Blake Snell</t>
+          <t>Martín Pérez</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>605483</t>
+          <t>527048</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -48402,22 +48402,22 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>31.4</v>
+        <v>25.2</v>
       </c>
       <c r="Q150" t="n">
-        <v>1.1</v>
+        <v>39</v>
       </c>
       <c r="R150" t="n">
-        <v>66.2</v>
+        <v>52.6</v>
       </c>
       <c r="S150" t="n">
-        <v>81.90000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="T150" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U150" t="n">
-        <v>18</v>
+        <v>10.6</v>
       </c>
       <c r="V150" t="n">
         <v>50</v>
@@ -48435,7 +48435,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -48477,12 +48477,12 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AL150" t="inlineStr">
@@ -48492,12 +48492,12 @@
       </c>
       <c r="AM150" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 0 HR</t>
+          <t>Last 7 games: 4/21, 0 HR</t>
         </is>
       </c>
       <c r="AN150" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.7% barrel, 0.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 9.5 HR allowed</t>
         </is>
       </c>
       <c r="AO150" t="inlineStr">
@@ -48507,102 +48507,102 @@
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="AQ150" t="inlineStr">
         <is>
-          <t>39.61</t>
+          <t>33.85</t>
         </is>
       </c>
       <c r="AR150" t="inlineStr">
         <is>
-          <t>87.47</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr">
         <is>
-          <t>100.1299</t>
+          <t>99.1033</t>
         </is>
       </c>
       <c r="AT150" t="inlineStr">
         <is>
-          <t>0.3862</t>
+          <t>0.3418</t>
         </is>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>0.1533</t>
+          <t>0.1308</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>0.3067</t>
+          <t>0.2717</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>72.51</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>26.04</t>
+          <t>32.44</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>42.39</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>31.18</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>0.1512</t>
+          <t>0.1001</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>8.42</t>
         </is>
       </c>
       <c r="BD150" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="BE150" t="inlineStr">
         <is>
-          <t>84.38</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="BF150" t="inlineStr">
         <is>
-          <t>0.2793</t>
+          <t>0.4157</t>
         </is>
       </c>
       <c r="BG150" t="inlineStr">
         <is>
-          <t>0.0651</t>
+          <t>0.1639</t>
         </is>
       </c>
       <c r="BH150" t="inlineStr">
         <is>
-          <t>21.26</t>
+          <t>24.27</t>
         </is>
       </c>
       <c r="BI150" t="inlineStr">
         <is>
-          <t>144 deg</t>
+          <t>330 deg</t>
         </is>
       </c>
       <c r="BJ150" t="inlineStr">
@@ -48612,27 +48612,27 @@
       </c>
       <c r="BK150" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=39.7559&amp;lon=-104.9942</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
         </is>
       </c>
       <c r="BL150" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>43</t>
         </is>
       </c>
       <c r="BM150" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN150" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BO150" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BP150" t="inlineStr"/>
@@ -48653,27 +48653,27 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>641680</t>
+          <t>650489</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Jonah Heim</t>
+          <t>Willi Castro</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-08-17T23:40:00Z</t>
+          <t>2026-08-18T00:40:00Z</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -48683,26 +48683,26 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Blake Snell</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>608379</t>
+          <t>605483</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>39.8</v>
+        <v>40.1</v>
       </c>
       <c r="M151" t="inlineStr">
         <is>
@@ -48720,22 +48720,22 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>24.7</v>
+        <v>31.4</v>
       </c>
       <c r="Q151" t="n">
-        <v>35.4</v>
+        <v>1.1</v>
       </c>
       <c r="R151" t="n">
-        <v>50.7</v>
+        <v>66.2</v>
       </c>
       <c r="S151" t="n">
-        <v>59.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T151" t="n">
         <v>75</v>
       </c>
       <c r="U151" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="V151" t="n">
         <v>50</v>
@@ -48753,7 +48753,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -48795,7 +48795,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -48810,12 +48810,12 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/25, 0 HR</t>
+          <t>Last 7 games: 6/25, 0 HR</t>
         </is>
       </c>
       <c r="AN151" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.9% barrel, 17.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.7% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
@@ -48825,102 +48825,102 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>7.76</t>
         </is>
       </c>
       <c r="AQ151" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>39.61</t>
         </is>
       </c>
       <c r="AR151" t="inlineStr">
         <is>
-          <t>87.82</t>
+          <t>87.47</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr">
         <is>
-          <t>97.9919</t>
+          <t>100.1299</t>
         </is>
       </c>
       <c r="AT151" t="inlineStr">
         <is>
-          <t>0.3726</t>
+          <t>0.3862</t>
         </is>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>0.1431</t>
+          <t>0.1533</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>0.2921</t>
+          <t>0.3067</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>69.77</t>
+          <t>72.51</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>26.04</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>40.49</t>
+          <t>42.39</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>29.02</t>
+          <t>31.18</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>0.1659</t>
+          <t>0.1512</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BD151" t="inlineStr">
         <is>
-          <t>35.93</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="BE151" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>84.38</t>
         </is>
       </c>
       <c r="BF151" t="inlineStr">
         <is>
-          <t>0.4144</t>
+          <t>0.2793</t>
         </is>
       </c>
       <c r="BG151" t="inlineStr">
         <is>
-          <t>0.1633</t>
+          <t>0.0651</t>
         </is>
       </c>
       <c r="BH151" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>21.26</t>
         </is>
       </c>
       <c r="BI151" t="inlineStr">
         <is>
-          <t>354 deg</t>
+          <t>144 deg</t>
         </is>
       </c>
       <c r="BJ151" t="inlineStr">
@@ -48930,27 +48930,27 @@
       </c>
       <c r="BK151" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=39.0517&amp;lon=-94.4803</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=39.7559&amp;lon=-104.9942</t>
         </is>
       </c>
       <c r="BL151" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>49</t>
         </is>
       </c>
       <c r="BM151" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="BN151" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BO151" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BP151" t="inlineStr"/>
@@ -48971,27 +48971,27 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>593871</t>
+          <t>641680</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Jorge Polanco</t>
+          <t>Jonah Heim</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-08-17T23:10:00Z</t>
+          <t>2026-08-17T23:40:00Z</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -49001,17 +49001,17 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Walker Buehler</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>621111</t>
+          <t>608379</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -49020,7 +49020,7 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>39.7</v>
+        <v>39.8</v>
       </c>
       <c r="M152" t="inlineStr">
         <is>
@@ -49038,22 +49038,22 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>21.5</v>
+        <v>24.7</v>
       </c>
       <c r="Q152" t="n">
-        <v>40.9</v>
+        <v>35.4</v>
       </c>
       <c r="R152" t="n">
-        <v>49.3</v>
+        <v>50.7</v>
       </c>
       <c r="S152" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T152" t="n">
         <v>75</v>
       </c>
       <c r="U152" t="n">
-        <v>30.3</v>
+        <v>0</v>
       </c>
       <c r="V152" t="n">
         <v>50</v>
@@ -49071,7 +49071,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -49113,7 +49113,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
@@ -49123,17 +49123,17 @@
       </c>
       <c r="AL152" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 1 HR</t>
+          <t>Last 7 games: 3/25, 0 HR</t>
         </is>
       </c>
       <c r="AN152" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.7% barrel, 16.4 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.9% barrel, 17.1 HR allowed</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
@@ -49143,102 +49143,102 @@
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="AQ152" t="inlineStr">
         <is>
-          <t>36.14</t>
+          <t>33.31</t>
         </is>
       </c>
       <c r="AR152" t="inlineStr">
         <is>
-          <t>87.58</t>
+          <t>87.82</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr">
         <is>
-          <t>98.6767</t>
+          <t>97.9919</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr">
         <is>
-          <t>0.3359</t>
+          <t>0.3726</t>
         </is>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>0.1273</t>
+          <t>0.1431</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>0.2646</t>
+          <t>0.2921</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>69.77</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>40.49</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>29.02</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>0.1271</t>
+          <t>0.1659</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>8.73</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="BD152" t="inlineStr">
         <is>
-          <t>39.13</t>
+          <t>35.93</t>
         </is>
       </c>
       <c r="BE152" t="inlineStr">
         <is>
-          <t>88.95</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BF152" t="inlineStr">
         <is>
-          <t>0.4164</t>
+          <t>0.4144</t>
         </is>
       </c>
       <c r="BG152" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>0.1633</t>
         </is>
       </c>
       <c r="BH152" t="inlineStr">
         <is>
-          <t>23.23</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="BI152" t="inlineStr">
         <is>
-          <t>191 deg</t>
+          <t>354 deg</t>
         </is>
       </c>
       <c r="BJ152" t="inlineStr">
@@ -49248,27 +49248,27 @@
       </c>
       <c r="BK152" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=40.7571&amp;lon=-73.8458</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=39.0517&amp;lon=-94.4803</t>
         </is>
       </c>
       <c r="BL152" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BM152" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="BN152" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BO152" t="inlineStr">
         <is>
-          <t>Citi Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BP152" t="inlineStr"/>
@@ -49289,27 +49289,27 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>622268</t>
+          <t>593871</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Donovan Walton</t>
+          <t>Jorge Polanco</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-08-17T23:40:00Z</t>
+          <t>2026-08-17T23:10:00Z</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -49319,17 +49319,17 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Walker Buehler</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>608379</t>
+          <t>621111</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
@@ -49356,22 +49356,22 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>13.8</v>
+        <v>21.5</v>
       </c>
       <c r="Q153" t="n">
-        <v>37.3</v>
+        <v>40.9</v>
       </c>
       <c r="R153" t="n">
-        <v>50.7</v>
+        <v>49.3</v>
       </c>
       <c r="S153" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T153" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U153" t="n">
-        <v>16.6</v>
+        <v>30.3</v>
       </c>
       <c r="V153" t="n">
         <v>50</v>
@@ -49389,7 +49389,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -49431,27 +49431,27 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL153" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/13, 0 HR</t>
+          <t>Last 7 games: 5/25, 1 HR</t>
         </is>
       </c>
       <c r="AN153" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 17.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.7% barrel, 16.4 HR allowed</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
@@ -49461,102 +49461,102 @@
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="AQ153" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>36.14</t>
         </is>
       </c>
       <c r="AR153" t="inlineStr">
         <is>
-          <t>88.96</t>
+          <t>87.58</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr">
         <is>
-          <t>97.6604</t>
+          <t>98.6767</t>
         </is>
       </c>
       <c r="AT153" t="inlineStr">
         <is>
-          <t>0.3555</t>
+          <t>0.3359</t>
         </is>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>0.0942</t>
+          <t>0.1273</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>0.2646</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>67.64</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>37.77</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>19.78</t>
+          <t>25.2</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>0.1099</t>
+          <t>0.1271</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>8.73</t>
         </is>
       </c>
       <c r="BD153" t="inlineStr">
         <is>
-          <t>35.93</t>
+          <t>39.13</t>
         </is>
       </c>
       <c r="BE153" t="inlineStr">
         <is>
-          <t>88.27</t>
+          <t>88.95</t>
         </is>
       </c>
       <c r="BF153" t="inlineStr">
         <is>
-          <t>0.4144</t>
+          <t>0.4164</t>
         </is>
       </c>
       <c r="BG153" t="inlineStr">
         <is>
-          <t>0.1633</t>
+          <t>0.161</t>
         </is>
       </c>
       <c r="BH153" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>23.23</t>
         </is>
       </c>
       <c r="BI153" t="inlineStr">
         <is>
-          <t>354 deg</t>
+          <t>191 deg</t>
         </is>
       </c>
       <c r="BJ153" t="inlineStr">
@@ -49566,27 +49566,27 @@
       </c>
       <c r="BK153" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=39.0517&amp;lon=-94.4803</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=40.7571&amp;lon=-73.8458</t>
         </is>
       </c>
       <c r="BL153" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM153" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BN153" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BO153" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Citi Field</t>
         </is>
       </c>
       <c r="BP153" t="inlineStr"/>
@@ -49607,27 +49607,27 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>669364</t>
+          <t>622268</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Xavier Edwards</t>
+          <t>Donovan Walton</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-08-17T22:40:00Z</t>
+          <t>2026-08-17T23:40:00Z</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -49637,26 +49637,26 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Cristopher Sánchez</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>650911</t>
+          <t>608379</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>39.5</v>
+        <v>39.7</v>
       </c>
       <c r="M154" t="inlineStr">
         <is>
@@ -49670,26 +49670,26 @@
       </c>
       <c r="O154" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P154" t="n">
-        <v>9.5</v>
+        <v>13.8</v>
       </c>
       <c r="Q154" t="n">
-        <v>30.8</v>
+        <v>37.3</v>
       </c>
       <c r="R154" t="n">
-        <v>52.8</v>
+        <v>50.7</v>
       </c>
       <c r="S154" t="n">
-        <v>90.40000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="T154" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U154" t="n">
-        <v>18</v>
+        <v>16.6</v>
       </c>
       <c r="V154" t="n">
         <v>50</v>
@@ -49707,7 +49707,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -49749,12 +49749,12 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AL154" t="inlineStr">
@@ -49764,12 +49764,12 @@
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 0 HR</t>
+          <t>Last 7 games: 3/13, 0 HR</t>
         </is>
       </c>
       <c r="AN154" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.0% barrel, 12.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 17.1 HR allowed</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
@@ -49779,102 +49779,102 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="AQ154" t="inlineStr">
         <is>
-          <t>29.05</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="AR154" t="inlineStr">
         <is>
-          <t>86.94</t>
+          <t>88.96</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr">
         <is>
-          <t>96.6117</t>
+          <t>97.6604</t>
         </is>
       </c>
       <c r="AT154" t="inlineStr">
         <is>
-          <t>0.3565</t>
+          <t>0.3555</t>
         </is>
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>0.0928</t>
+          <t>0.0942</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>0.3111</t>
+          <t>0.302</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>68.02</t>
+          <t>67.64</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>29.08</t>
+          <t>37.77</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>21.91</t>
+          <t>19.78</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>0.0917</t>
+          <t>0.1099</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>6.96</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="BD154" t="inlineStr">
         <is>
-          <t>41.41</t>
+          <t>35.93</t>
         </is>
       </c>
       <c r="BE154" t="inlineStr">
         <is>
-          <t>89.14</t>
+          <t>88.27</t>
         </is>
       </c>
       <c r="BF154" t="inlineStr">
         <is>
-          <t>0.3548</t>
+          <t>0.4144</t>
         </is>
       </c>
       <c r="BG154" t="inlineStr">
         <is>
-          <t>0.1228</t>
+          <t>0.1633</t>
         </is>
       </c>
       <c r="BH154" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="BI154" t="inlineStr">
         <is>
-          <t>106 deg</t>
+          <t>354 deg</t>
         </is>
       </c>
       <c r="BJ154" t="inlineStr">
@@ -49884,27 +49884,27 @@
       </c>
       <c r="BK154" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=39.9061&amp;lon=-75.1665</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=39.0517&amp;lon=-94.4803</t>
         </is>
       </c>
       <c r="BL154" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="BM154" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="BN154" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="BM154" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="BN154" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
       <c r="BO154" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BP154" t="inlineStr"/>
@@ -49925,27 +49925,27 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>680779</t>
+          <t>669364</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Henry Davis</t>
+          <t>Xavier Edwards</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-08-17T23:05:00Z</t>
+          <t>2026-08-17T22:40:00Z</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -49955,17 +49955,17 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Framber Valdez</t>
+          <t>Cristopher Sánchez</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>664285</t>
+          <t>650911</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -49988,26 +49988,26 @@
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P155" t="n">
-        <v>35</v>
+        <v>9.5</v>
       </c>
       <c r="Q155" t="n">
-        <v>35.6</v>
+        <v>30.8</v>
       </c>
       <c r="R155" t="n">
-        <v>42.8</v>
+        <v>52.8</v>
       </c>
       <c r="S155" t="n">
-        <v>40.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T155" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U155" t="n">
-        <v>2.5</v>
+        <v>18</v>
       </c>
       <c r="V155" t="n">
         <v>50</v>
@@ -50025,7 +50025,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -50067,12 +50067,12 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL155" t="inlineStr">
@@ -50082,12 +50082,12 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/22, 0 HR</t>
+          <t>Last 7 games: 6/25, 0 HR</t>
         </is>
       </c>
       <c r="AN155" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 13.6 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.0% barrel, 12.7 HR allowed</t>
         </is>
       </c>
       <c r="AO155" t="inlineStr">
@@ -50097,102 +50097,102 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>9.68</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="AQ155" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="AR155" t="inlineStr">
         <is>
-          <t>89.51</t>
+          <t>86.94</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr">
         <is>
-          <t>100.4627</t>
+          <t>96.6117</t>
         </is>
       </c>
       <c r="AT155" t="inlineStr">
         <is>
-          <t>0.3505</t>
+          <t>0.3565</t>
         </is>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>0.0928</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>0.2853</t>
+          <t>0.3111</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>68.02</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>42.63</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>50.02</t>
+          <t>29.08</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>21.91</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>0.1257</t>
+          <t>0.0917</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>6.96</t>
         </is>
       </c>
       <c r="BD155" t="inlineStr">
         <is>
-          <t>44.06</t>
+          <t>41.41</t>
         </is>
       </c>
       <c r="BE155" t="inlineStr">
         <is>
-          <t>90.24</t>
+          <t>89.14</t>
         </is>
       </c>
       <c r="BF155" t="inlineStr">
         <is>
-          <t>0.384</t>
+          <t>0.3548</t>
         </is>
       </c>
       <c r="BG155" t="inlineStr">
         <is>
-          <t>0.1325</t>
+          <t>0.1228</t>
         </is>
       </c>
       <c r="BH155" t="inlineStr">
         <is>
-          <t>18.67</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="BI155" t="inlineStr">
         <is>
-          <t>221 deg</t>
+          <t>106 deg</t>
         </is>
       </c>
       <c r="BJ155" t="inlineStr">
@@ -50202,27 +50202,27 @@
       </c>
       <c r="BK155" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=40.4469&amp;lon=-80.0057</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=39.9061&amp;lon=-75.1665</t>
         </is>
       </c>
       <c r="BL155" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BM155" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>15</t>
         </is>
       </c>
       <c r="BN155" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BO155" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BP155" t="inlineStr"/>
@@ -50243,27 +50243,27 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>543760</t>
+          <t>680779</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Marcus Semien</t>
+          <t>Henry Davis</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-08-17T23:10:00Z</t>
+          <t>2026-08-17T23:05:00Z</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -50273,22 +50273,22 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Walker Buehler</t>
+          <t>Framber Valdez</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>621111</t>
+          <t>664285</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L156" t="n">
@@ -50306,26 +50306,26 @@
       </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P156" t="n">
-        <v>25.2</v>
+        <v>35</v>
       </c>
       <c r="Q156" t="n">
-        <v>42.7</v>
+        <v>35.6</v>
       </c>
       <c r="R156" t="n">
-        <v>49.3</v>
+        <v>42.8</v>
       </c>
       <c r="S156" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T156" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U156" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="V156" t="n">
         <v>50</v>
@@ -50343,7 +50343,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -50390,7 +50390,7 @@
       </c>
       <c r="AK156" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AL156" t="inlineStr">
@@ -50400,12 +50400,12 @@
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/24, 0 HR</t>
+          <t>Last 7 games: 3/22, 0 HR</t>
         </is>
       </c>
       <c r="AN156" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 16.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 13.6 HR allowed</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
@@ -50415,102 +50415,102 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>9.68</t>
         </is>
       </c>
       <c r="AQ156" t="inlineStr">
         <is>
-          <t>34.79</t>
+          <t>38.59</t>
         </is>
       </c>
       <c r="AR156" t="inlineStr">
         <is>
-          <t>86.97</t>
+          <t>89.51</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr">
         <is>
-          <t>97.5774</t>
+          <t>100.4627</t>
         </is>
       </c>
       <c r="AT156" t="inlineStr">
         <is>
-          <t>0.3929</t>
+          <t>0.3505</t>
         </is>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>0.1495</t>
+          <t>0.148</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>0.3075</t>
+          <t>0.2853</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>3.34</t>
+          <t>42.63</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>46.91</t>
+          <t>50.02</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>26.49</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>14.3</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1257</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>8.73</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="BD156" t="inlineStr">
         <is>
-          <t>39.13</t>
+          <t>44.06</t>
         </is>
       </c>
       <c r="BE156" t="inlineStr">
         <is>
-          <t>88.95</t>
+          <t>90.24</t>
         </is>
       </c>
       <c r="BF156" t="inlineStr">
         <is>
-          <t>0.4164</t>
+          <t>0.384</t>
         </is>
       </c>
       <c r="BG156" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>0.1325</t>
         </is>
       </c>
       <c r="BH156" t="inlineStr">
         <is>
-          <t>23.23</t>
+          <t>18.67</t>
         </is>
       </c>
       <c r="BI156" t="inlineStr">
         <is>
-          <t>191 deg</t>
+          <t>221 deg</t>
         </is>
       </c>
       <c r="BJ156" t="inlineStr">
@@ -50520,27 +50520,27 @@
       </c>
       <c r="BK156" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=40.7571&amp;lon=-73.8458</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=40.4469&amp;lon=-80.0057</t>
         </is>
       </c>
       <c r="BL156" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BM156" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>28</t>
         </is>
       </c>
       <c r="BN156" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO156" t="inlineStr">
         <is>
-          <t>Citi Field</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BP156" t="inlineStr"/>
@@ -50561,27 +50561,27 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>694249</t>
+          <t>543760</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Cole Carrigg</t>
+          <t>Marcus Semien</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-08-18T00:40:00Z</t>
+          <t>2026-08-17T23:10:00Z</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -50591,26 +50591,26 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Blake Snell</t>
+          <t>Walker Buehler</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>605483</t>
+          <t>621111</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>39.3</v>
+        <v>39.5</v>
       </c>
       <c r="M157" t="inlineStr">
         <is>
@@ -50624,26 +50624,26 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P157" t="n">
-        <v>22.2</v>
+        <v>25.2</v>
       </c>
       <c r="Q157" t="n">
-        <v>1.1</v>
+        <v>42.7</v>
       </c>
       <c r="R157" t="n">
-        <v>66.2</v>
+        <v>49.3</v>
       </c>
       <c r="S157" t="n">
-        <v>95.5</v>
+        <v>59.8</v>
       </c>
       <c r="T157" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U157" t="n">
-        <v>21.1</v>
+        <v>0.8</v>
       </c>
       <c r="V157" t="n">
         <v>50</v>
@@ -50661,7 +50661,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -50686,7 +50686,7 @@
       </c>
       <c r="AE157" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF157" t="inlineStr"/>
@@ -50703,12 +50703,12 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL157" t="inlineStr">
@@ -50718,12 +50718,12 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 0 HR</t>
+          <t>Last 7 games: 3/24, 0 HR</t>
         </is>
       </c>
       <c r="AN157" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.7% barrel, 0.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 16.4 HR allowed</t>
         </is>
       </c>
       <c r="AO157" t="inlineStr">
@@ -50733,102 +50733,102 @@
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="AQ157" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>34.79</t>
         </is>
       </c>
       <c r="AR157" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.97</t>
         </is>
       </c>
       <c r="AS157" t="inlineStr">
         <is>
-          <t>98.1473</t>
+          <t>97.5774</t>
         </is>
       </c>
       <c r="AT157" t="inlineStr">
         <is>
-          <t>0.399</t>
+          <t>0.3929</t>
         </is>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>0.1495</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>0.335</t>
+          <t>0.3075</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>3.34</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>46.91</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>31.44</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>14.3</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>8.73</t>
         </is>
       </c>
       <c r="BD157" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>39.13</t>
         </is>
       </c>
       <c r="BE157" t="inlineStr">
         <is>
-          <t>84.38</t>
+          <t>88.95</t>
         </is>
       </c>
       <c r="BF157" t="inlineStr">
         <is>
-          <t>0.2793</t>
+          <t>0.4164</t>
         </is>
       </c>
       <c r="BG157" t="inlineStr">
         <is>
-          <t>0.0651</t>
+          <t>0.161</t>
         </is>
       </c>
       <c r="BH157" t="inlineStr">
         <is>
-          <t>21.26</t>
+          <t>23.23</t>
         </is>
       </c>
       <c r="BI157" t="inlineStr">
         <is>
-          <t>144 deg</t>
+          <t>191 deg</t>
         </is>
       </c>
       <c r="BJ157" t="inlineStr">
@@ -50838,27 +50838,27 @@
       </c>
       <c r="BK157" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=39.7559&amp;lon=-104.9942</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=40.7571&amp;lon=-73.8458</t>
         </is>
       </c>
       <c r="BL157" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>71</t>
         </is>
       </c>
       <c r="BM157" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="BN157" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BO157" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Citi Field</t>
         </is>
       </c>
       <c r="BP157" t="inlineStr"/>
@@ -50879,47 +50879,47 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>669911</t>
+          <t>694249</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Michael Toglia</t>
+          <t>Cole Carrigg</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-08-17T17:40:00Z</t>
+          <t>2026-08-18T00:40:00Z</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Quinn Mathews</t>
+          <t>Blake Snell</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>687273</t>
+          <t>605483</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -50928,7 +50928,7 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
       </c>
       <c r="M158" t="inlineStr">
         <is>
@@ -50942,26 +50942,26 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>Good Environment, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P158" t="n">
-        <v>22.6</v>
+        <v>22.2</v>
       </c>
       <c r="Q158" t="n">
-        <v>7.2</v>
+        <v>1.1</v>
       </c>
       <c r="R158" t="n">
-        <v>78.3</v>
+        <v>66.2</v>
       </c>
       <c r="S158" t="n">
-        <v>76.2</v>
+        <v>95.5</v>
       </c>
       <c r="T158" t="n">
         <v>75</v>
       </c>
       <c r="U158" t="n">
-        <v>7</v>
+        <v>21.1</v>
       </c>
       <c r="V158" t="n">
         <v>50</v>
@@ -50969,38 +50969,42 @@
       <c r="W158" t="inlineStr"/>
       <c r="X158" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Y158" t="inlineStr">
+      <c r="AB158" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AA158" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AD158" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AD158" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AE158" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF158" t="inlineStr"/>
@@ -51012,17 +51016,17 @@
       </c>
       <c r="AI158" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AL158" t="inlineStr">
@@ -51032,117 +51036,117 @@
       </c>
       <c r="AM158" t="inlineStr">
         <is>
-          <t>Last 5 games: 2/12, 0 HR</t>
+          <t>Last 7 games: 6/23, 0 HR</t>
         </is>
       </c>
       <c r="AN158" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.7% barrel, 0.9 HR allowed</t>
         </is>
       </c>
       <c r="AO158" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="AQ158" t="inlineStr">
         <is>
-          <t>42.99</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="AR158" t="inlineStr">
         <is>
-          <t>89.69</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AS158" t="inlineStr">
         <is>
-          <t>97.4919</t>
+          <t>98.1473</t>
         </is>
       </c>
       <c r="AT158" t="inlineStr">
         <is>
-          <t>0.2467</t>
+          <t>0.399</t>
         </is>
       </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>0.0638</t>
+          <t>0.134</t>
         </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
-          <t>0.2248</t>
+          <t>0.335</t>
         </is>
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>72.84</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>35.62</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>38.55</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>0.194</t>
         </is>
       </c>
       <c r="BC158" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BD158" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="BE158" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>84.38</t>
         </is>
       </c>
       <c r="BF158" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>0.2793</t>
         </is>
       </c>
       <c r="BG158" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>0.0651</t>
         </is>
       </c>
       <c r="BH158" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>21.26</t>
         </is>
       </c>
       <c r="BI158" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>144 deg</t>
         </is>
       </c>
       <c r="BJ158" t="inlineStr">
@@ -51152,27 +51156,27 @@
       </c>
       <c r="BK158" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=39.0979&amp;lon=-84.5082</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=39.7559&amp;lon=-104.9942</t>
         </is>
       </c>
       <c r="BL158" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>49</t>
         </is>
       </c>
       <c r="BM158" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="BN158" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>78</t>
         </is>
       </c>
       <c r="BO158" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BP158" t="inlineStr"/>
@@ -51193,52 +51197,52 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>805347</t>
+          <t>669911</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Jim Jarvis</t>
+          <t>Michael Toglia</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-08-17T23:40:00Z</t>
+          <t>2026-08-17T17:40:00Z</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Bailey Ober</t>
+          <t>Quinn Mathews</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>641927</t>
+          <t>687273</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L159" t="n">
@@ -51256,26 +51260,26 @@
       </c>
       <c r="O159" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Good Environment, Platoon Edge</t>
         </is>
       </c>
       <c r="P159" t="n">
-        <v>14.5</v>
+        <v>22.6</v>
       </c>
       <c r="Q159" t="n">
-        <v>55.5</v>
+        <v>7.2</v>
       </c>
       <c r="R159" t="n">
-        <v>52.6</v>
+        <v>78.3</v>
       </c>
       <c r="S159" t="n">
-        <v>40.2</v>
+        <v>76.2</v>
       </c>
       <c r="T159" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U159" t="n">
-        <v>0.8</v>
+        <v>7</v>
       </c>
       <c r="V159" t="n">
         <v>50</v>
@@ -51283,42 +51287,38 @@
       <c r="W159" t="inlineStr"/>
       <c r="X159" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Y159" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AA159" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AD159" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AD159" t="inlineStr"/>
       <c r="AE159" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AF159" t="inlineStr"/>
@@ -51330,7 +51330,7 @@
       </c>
       <c r="AI159" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AJ159" t="inlineStr">
@@ -51340,7 +51340,7 @@
       </c>
       <c r="AK159" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AL159" t="inlineStr">
@@ -51350,117 +51350,117 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Last 5 games: 2/12, 0 HR</t>
         </is>
       </c>
       <c r="AN159" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.7% barrel, 20.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AO159" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>fly-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="AQ159" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>42.99</t>
         </is>
       </c>
       <c r="AR159" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.69</t>
         </is>
       </c>
       <c r="AS159" t="inlineStr">
         <is>
-          <t>98.5322</t>
+          <t>97.4919</t>
         </is>
       </c>
       <c r="AT159" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>0.2467</t>
         </is>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>0.0638</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>0.2248</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.84</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>35.62</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>26.7</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>38.55</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>0.107</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="BD159" t="inlineStr">
         <is>
-          <t>36.23</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="BE159" t="inlineStr">
         <is>
-          <t>88.83</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="BF159" t="inlineStr">
         <is>
-          <t>0.4669</t>
+          <t>0.288</t>
         </is>
       </c>
       <c r="BG159" t="inlineStr">
         <is>
-          <t>0.2147</t>
+          <t>0.041</t>
         </is>
       </c>
       <c r="BH159" t="inlineStr">
         <is>
-          <t>31.83</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="BI159" t="inlineStr">
         <is>
-          <t>330 deg</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BJ159" t="inlineStr">
@@ -51470,27 +51470,27 @@
       </c>
       <c r="BK159" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=39.0979&amp;lon=-84.5082</t>
         </is>
       </c>
       <c r="BL159" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BM159" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="BN159" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BO159" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BP159" t="inlineStr"/>
@@ -51511,24 +51511,24 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>807712</t>
+          <t>805347</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Luke Keaschall</t>
+          <t>Jim Jarvis</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
           <t>MIN</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F160" t="inlineStr">
         <is>
           <t>2026-08-17T23:40:00Z</t>
@@ -51541,22 +51541,22 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Martín Pérez</t>
+          <t>Bailey Ober</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>527048</t>
+          <t>641927</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L160" t="n">
@@ -51578,22 +51578,22 @@
         </is>
       </c>
       <c r="P160" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="Q160" t="n">
-        <v>39</v>
+        <v>55.5</v>
       </c>
       <c r="R160" t="n">
         <v>52.6</v>
       </c>
       <c r="S160" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T160" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U160" t="n">
-        <v>43.2</v>
+        <v>0.8</v>
       </c>
       <c r="V160" t="n">
         <v>50</v>
@@ -51611,7 +51611,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -51636,7 +51636,7 @@
       </c>
       <c r="AE160" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AF160" t="inlineStr"/>
@@ -51653,127 +51653,127 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AL160" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM160" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 1 HR</t>
+          <t>Last 7 games: 2/16, 0 HR</t>
         </is>
       </c>
       <c r="AN160" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 9.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.7% barrel, 20.9 HR allowed</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="AQ160" t="inlineStr">
         <is>
-          <t>29.87</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="AR160" t="inlineStr">
         <is>
-          <t>85.29</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AS160" t="inlineStr">
         <is>
-          <t>96.7373</t>
+          <t>98.5322</t>
         </is>
       </c>
       <c r="AT160" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.311</t>
         </is>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>0.1104</t>
+          <t>0.071</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>0.3149</t>
+          <t>0.268</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>68.64</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>7.73</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>38.96</t>
+          <t>26.7</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>26.69</t>
+          <t>18.6</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>0.1171</t>
+          <t>0.097</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>8.42</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="BD160" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>36.23</t>
         </is>
       </c>
       <c r="BE160" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.83</t>
         </is>
       </c>
       <c r="BF160" t="inlineStr">
         <is>
-          <t>0.4157</t>
+          <t>0.4669</t>
         </is>
       </c>
       <c r="BG160" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.2147</t>
         </is>
       </c>
       <c r="BH160" t="inlineStr">
         <is>
-          <t>24.27</t>
+          <t>31.83</t>
         </is>
       </c>
       <c r="BI160" t="inlineStr">
